--- a/research/traditional_assets/database/data/czech_republic/czech_republic_metals_mining.xlsx
+++ b/research/traditional_assets/database/data/czech_republic/czech_republic_metals_mining.xlsx
@@ -588,7 +588,7 @@
         </is>
       </c>
       <c r="K2">
-        <v>-0.03</v>
+        <v>-0.278</v>
       </c>
       <c r="M2">
         <v>0</v>
@@ -618,61 +618,61 @@
         <v>0</v>
       </c>
       <c r="W2">
-        <v>0.4918032786885246</v>
+        <v>3.054945054945055</v>
       </c>
       <c r="X2">
-        <v>0.06402028865373496</v>
+        <v>0.1549033842420518</v>
       </c>
       <c r="Y2">
-        <v>0.4277829900347896</v>
+        <v>2.900041670703003</v>
       </c>
       <c r="Z2">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA2">
-        <v>0.7173913043478262</v>
+        <v>-0.4166666666666667</v>
       </c>
       <c r="AB2">
-        <v>0.06195619088833912</v>
+        <v>0.1161754680271359</v>
       </c>
       <c r="AC2">
-        <v>0.655435113459487</v>
+        <v>-0.5328421346938027</v>
       </c>
       <c r="AD2">
-        <v>0.175</v>
+        <v>0.193</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>0.175</v>
+        <v>0.193</v>
       </c>
       <c r="AG2">
-        <v>0.175</v>
+        <v>0.193</v>
       </c>
       <c r="AH2">
-        <v>0.05942275042444822</v>
+        <v>0.3821782178217822</v>
       </c>
       <c r="AI2">
-        <v>2.083333333333333</v>
+        <v>-1.096590909090909</v>
       </c>
       <c r="AJ2">
-        <v>0.05942275042444822</v>
+        <v>0.3821782178217822</v>
       </c>
       <c r="AK2">
-        <v>2.083333333333333</v>
+        <v>-1.096590909090909</v>
       </c>
       <c r="AL2">
-        <v>0.001</v>
+        <v>0.007</v>
       </c>
       <c r="AM2">
-        <v>0.001</v>
+        <v>0.007</v>
       </c>
       <c r="AO2">
-        <v>-33</v>
+        <v>-5</v>
       </c>
       <c r="AQ2">
-        <v>-33</v>
+        <v>-5</v>
       </c>
     </row>
     <row r="3">
@@ -692,7 +692,7 @@
         </is>
       </c>
       <c r="K3">
-        <v>-0.03</v>
+        <v>-0.278</v>
       </c>
       <c r="M3">
         <v>-0</v>
@@ -722,61 +722,61 @@
         <v>0</v>
       </c>
       <c r="W3">
-        <v>0.4918032786885246</v>
+        <v>3.054945054945055</v>
       </c>
       <c r="X3">
-        <v>0.06402028865373496</v>
+        <v>0.1549033842420518</v>
       </c>
       <c r="Y3">
-        <v>0.4277829900347896</v>
+        <v>2.900041670703003</v>
       </c>
       <c r="Z3">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA3">
-        <v>0.7173913043478262</v>
+        <v>-0.4166666666666667</v>
       </c>
       <c r="AB3">
-        <v>0.06195619088833912</v>
+        <v>0.1161754680271359</v>
       </c>
       <c r="AC3">
-        <v>0.655435113459487</v>
+        <v>-0.5328421346938027</v>
       </c>
       <c r="AD3">
-        <v>0.175</v>
+        <v>0.193</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>0.175</v>
+        <v>0.193</v>
       </c>
       <c r="AG3">
-        <v>0.175</v>
+        <v>0.193</v>
       </c>
       <c r="AH3">
-        <v>0.05942275042444822</v>
+        <v>0.3821782178217822</v>
       </c>
       <c r="AI3">
-        <v>2.083333333333333</v>
+        <v>-1.096590909090909</v>
       </c>
       <c r="AJ3">
-        <v>0.05942275042444822</v>
+        <v>0.3821782178217822</v>
       </c>
       <c r="AK3">
-        <v>2.083333333333333</v>
+        <v>-1.096590909090909</v>
       </c>
       <c r="AL3">
-        <v>0.001</v>
+        <v>0.007</v>
       </c>
       <c r="AM3">
-        <v>0.001</v>
+        <v>0.007</v>
       </c>
       <c r="AO3">
-        <v>-33</v>
+        <v>-5</v>
       </c>
       <c r="AQ3">
-        <v>-33</v>
+        <v>-5</v>
       </c>
     </row>
   </sheetData>
